--- a/files/港岛-山顶区-Mount Nicholson II.xlsx
+++ b/files/港岛-山顶区-Mount Nicholson II.xlsx
@@ -8,8 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="A座 销控表" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="B座 销控表" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -43,65 +41,8 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00002060"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00660000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00660000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -112,42 +53,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9F5A9"/>
-        <bgColor rgb="00A9F5A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9D0F5"/>
-        <bgColor rgb="00A9D0F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F5A9A9"/>
-        <bgColor rgb="00F5A9A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC000"/>
-        <bgColor rgb="00FFC000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E5E5E5"/>
-        <bgColor rgb="00E5E5E5"/>
       </patternFill>
     </fill>
   </fills>
@@ -177,7 +82,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -193,45 +98,6 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -598,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J26"/>
+  <dimension ref="A1:J28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -979,7 +845,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-11-07</t>
         </is>
       </c>
       <c r="H9" s="5" t="n">
@@ -1025,7 +891,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2016-12-08</t>
         </is>
       </c>
       <c r="H10" s="5" t="n">
@@ -1117,7 +983,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2017-02-22</t>
         </is>
       </c>
       <c r="H12" s="5" t="n">
@@ -1351,7 +1217,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-04-28</t>
         </is>
       </c>
       <c r="H17" s="5" t="n">
@@ -1535,7 +1401,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-12-13</t>
         </is>
       </c>
       <c r="H21" s="5" t="n">
@@ -1581,7 +1447,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-11-13</t>
         </is>
       </c>
       <c r="H22" s="5" t="n">
@@ -1673,7 +1539,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2017-07-13</t>
         </is>
       </c>
       <c r="H24" s="5" t="n">
@@ -1775,6 +1641,98 @@
         <v>144415</v>
       </c>
       <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>21号屋</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="n">
+        <v>6326</v>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>2019-08-01</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="n">
+        <v>538899288</v>
+      </c>
+      <c r="I27" s="5" t="n">
+        <v>85188</v>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>22号屋</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="n">
+        <v>7008</v>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>2019-09-12</t>
+        </is>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>580888000</v>
+      </c>
+      <c r="I28" s="5" t="n">
+        <v>82889</v>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -1787,610 +1745,4 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F17"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Mount Nicholson II - A座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>12 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>11 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>1 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>- | 4493呎 (4+房)
-$91,200万
-$202,982/呎
-(16年-11月)</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr"/>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>- | 4538呎 (4+房)
-$68,578万
-$151,119/呎
-(16年-10月)</t>
-        </is>
-      </c>
-      <c r="C7" s="17" t="inlineStr"/>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
-        <is>
-          <t>- | 4548呎 (4+房)
-$74,902万
-$164,692/呎
-(16年-10月)</t>
-        </is>
-      </c>
-      <c r="C8" s="17" t="inlineStr"/>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
-        <is>
-          <t>- | 4566呎 (4+房)
-$65,200万
-$142,795/呎
-(16年-10月)</t>
-        </is>
-      </c>
-      <c r="C9" s="17" t="inlineStr"/>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
-        <is>
-          <t>- | 4566呎 (4+房)
-$64,464万
-$141,184/呎
-(16年-10月)</t>
-        </is>
-      </c>
-      <c r="C10" s="17" t="inlineStr"/>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
-        <is>
-          <t>- | 4566呎 (4+房)
-$64,642万
-$141,571/呎
-(16年-10月)</t>
-        </is>
-      </c>
-      <c r="C11" s="17" t="inlineStr"/>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="inlineStr">
-        <is>
-          <t>- | 4566呎 (4+房)
-$35,039万
-$76,739/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C12" s="17" t="inlineStr"/>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="inlineStr">
-        <is>
-          <t>- | 4566呎 (4+房)
-$31,200万
-$68,331/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="C13" s="17" t="inlineStr"/>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="inlineStr">
-        <is>
-          <t>- | 4566呎 (4+房)
-$59,328万
-$129,935/呎
-(17年-01月)</t>
-        </is>
-      </c>
-      <c r="C14" s="17" t="inlineStr"/>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="inlineStr">
-        <is>
-          <t>- | 4566呎 (4+房)
-$30,820万
-$67,500/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C15" s="17" t="inlineStr"/>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="inlineStr">
-        <is>
-          <t>- | 4569呎 (4+房)
-$56,800万
-$124,316/呎
-(17年-03月)</t>
-        </is>
-      </c>
-      <c r="C16" s="17" t="inlineStr"/>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>PH/F</t>
-        </is>
-      </c>
-      <c r="B17" s="17" t="inlineStr"/>
-      <c r="C17" s="18" t="inlineStr">
-        <is>
-          <t>A | 4499呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F17"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Mount Nicholson II - B座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>12 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>12 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>- | 4209呎 (4+房)
-$91,200万
-$216,679/呎
-(16年-11月)</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr"/>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>- | 4254呎 (4+房)
-$68,578万
-$161,207/呎
-(16年-10月)</t>
-        </is>
-      </c>
-      <c r="C7" s="17" t="inlineStr"/>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
-        <is>
-          <t>- | 4264呎 (4+房)
-$38,000万
-$89,118/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C8" s="17" t="inlineStr"/>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
-        <is>
-          <t>- | 4289呎 (4+房)
-$65,200万
-$152,017/呎
-(16年-10月)</t>
-        </is>
-      </c>
-      <c r="C9" s="17" t="inlineStr"/>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
-        <is>
-          <t>- | 4289呎 (4+房)
-$64,464万
-$150,302/呎
-(16年-10月)</t>
-        </is>
-      </c>
-      <c r="C10" s="17" t="inlineStr"/>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
-        <is>
-          <t>- | 4289呎 (4+房)
-$64,642万
-$150,715/呎
-(16年-10月)</t>
-        </is>
-      </c>
-      <c r="C11" s="17" t="inlineStr"/>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="inlineStr">
-        <is>
-          <t>- | 4289呎 (4+房)
-$31,653万
-$73,800/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C12" s="17" t="inlineStr"/>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="inlineStr">
-        <is>
-          <t>- | 4289呎 (4+房)
-$27,278万
-$63,600/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C13" s="17" t="inlineStr"/>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="inlineStr">
-        <is>
-          <t>- | 4289呎 (4+房)
-$59,328万
-$138,327/呎
-(17年-01月)</t>
-        </is>
-      </c>
-      <c r="C14" s="17" t="inlineStr"/>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="inlineStr">
-        <is>
-          <t>- | 4289呎 (4+房)
-$28,736万
-$66,999/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C15" s="17" t="inlineStr"/>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="inlineStr">
-        <is>
-          <t>- | 4281呎 (4+房)
-$56,800万
-$132,679/呎
-(17年-03月)</t>
-        </is>
-      </c>
-      <c r="C16" s="17" t="inlineStr"/>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>PH/F</t>
-        </is>
-      </c>
-      <c r="B17" s="17" t="inlineStr"/>
-      <c r="C17" s="16" t="inlineStr">
-        <is>
-          <t>B | 4217呎 (4+房)
-$60,900万
-$144,415/呎
-(25年-06月)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/files/港岛-山顶区-Mount Nicholson II.xlsx
+++ b/files/港岛-山顶区-Mount Nicholson II.xlsx
@@ -8,6 +8,9 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="A座" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="B座" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="独立屋销控表" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +22,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="24">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,8 +44,120 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00002060"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00660000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00002060"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00660000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +168,42 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9F5A9"/>
+        <bgColor rgb="00A9F5A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9D0F5"/>
+        <bgColor rgb="00A9D0F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5A9A9"/>
+        <bgColor rgb="00F5A9A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC000"/>
+        <bgColor rgb="00FFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8E8E8"/>
+        <bgColor rgb="00E8E8E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -82,7 +233,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -97,6 +248,72 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -474,7 +691,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -1745,4 +1962,746 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>A座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>- | 4493呎 (4+房)
+$91200万
+$202,982/呎
+(16年-11月)</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>- | 4538呎 (4+房)
+$68578万
+$151,119/呎
+(16年-10月)</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>- | 4548呎 (4+房)
+$74902万
+$164,692/呎
+(16年-10月)</t>
+        </is>
+      </c>
+      <c r="C7" s="21" t="inlineStr"/>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>- | 4566呎 (4+房)
+$65200万
+$142,795/呎
+(16年-10月)</t>
+        </is>
+      </c>
+      <c r="C8" s="21" t="inlineStr"/>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>- | 4566呎 (4+房)
+$64464万
+$141,184/呎
+(16年-10月)</t>
+        </is>
+      </c>
+      <c r="C9" s="21" t="inlineStr"/>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>- | 4566呎 (4+房)
+$64642万
+$141,571/呎
+(16年-10月)</t>
+        </is>
+      </c>
+      <c r="C10" s="21" t="inlineStr"/>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>- | 4566呎 (4+房)
+$35039万
+$76,739/呎
+(16年-11月)</t>
+        </is>
+      </c>
+      <c r="C11" s="21" t="inlineStr"/>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>- | 4566呎 (4+房)
+$31200万
+$68,331/呎
+(16年-12月)</t>
+        </is>
+      </c>
+      <c r="C12" s="21" t="inlineStr"/>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>- | 4566呎 (4+房)
+$59328万
+$129,935/呎
+(17年-01月)</t>
+        </is>
+      </c>
+      <c r="C13" s="21" t="inlineStr"/>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>- | 4566呎 (4+房)
+$30820万
+$67,500/呎
+(17年-02月)</t>
+        </is>
+      </c>
+      <c r="C14" s="21" t="inlineStr"/>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>- | 4569呎 (4+房)
+$56800万
+$124,316/呎
+(17年-03月)</t>
+        </is>
+      </c>
+      <c r="C15" s="21" t="inlineStr"/>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>PH</t>
+        </is>
+      </c>
+      <c r="B16" s="21" t="inlineStr"/>
+      <c r="C16" s="22" t="inlineStr">
+        <is>
+          <t>A | 4499呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>B座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>- | 4209呎 (4+房)
+$91200万
+$216,679/呎
+(16年-11月)</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>- | 4254呎 (4+房)
+$68578万
+$161,207/呎
+(16年-10月)</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>- | 4264呎 (4+房)
+$38000万
+$89,118/呎
+(20年-04月)</t>
+        </is>
+      </c>
+      <c r="C7" s="21" t="inlineStr"/>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>- | 4289呎 (4+房)
+$65200万
+$152,017/呎
+(16年-10月)</t>
+        </is>
+      </c>
+      <c r="C8" s="21" t="inlineStr"/>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>- | 4289呎 (4+房)
+$64464万
+$150,302/呎
+(16年-10月)</t>
+        </is>
+      </c>
+      <c r="C9" s="21" t="inlineStr"/>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>- | 4289呎 (4+房)
+$64642万
+$150,715/呎
+(16年-10月)</t>
+        </is>
+      </c>
+      <c r="C10" s="21" t="inlineStr"/>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>- | 4289呎 (4+房)
+$31653万
+$73,800/呎
+(16年-12月)</t>
+        </is>
+      </c>
+      <c r="C11" s="21" t="inlineStr"/>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>- | 4289呎 (4+房)
+$27278万
+$63,600/呎
+(16年-11月)</t>
+        </is>
+      </c>
+      <c r="C12" s="21" t="inlineStr"/>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>- | 4289呎 (4+房)
+$59328万
+$138,327/呎
+(17年-01月)</t>
+        </is>
+      </c>
+      <c r="C13" s="21" t="inlineStr"/>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>- | 4289呎 (4+房)
+$28736万
+$66,999/呎
+(17年-07月)</t>
+        </is>
+      </c>
+      <c r="C14" s="21" t="inlineStr"/>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>- | 4281呎 (4+房)
+$56800万
+$132,679/呎
+(17年-03月)</t>
+        </is>
+      </c>
+      <c r="C15" s="21" t="inlineStr"/>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>PH</t>
+        </is>
+      </c>
+      <c r="B16" s="21" t="inlineStr"/>
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>B | 4217呎 (4+房)
+$60900万
+$144,415/呎
+(25年-06月)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="40" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Mount Nicholson II - 独立屋销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="12" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="25" customHeight="1">
+      <c r="A3" s="23" t="inlineStr">
+        <is>
+          <t>2 套</t>
+        </is>
+      </c>
+      <c r="B3" s="24" t="inlineStr">
+        <is>
+          <t>0 套</t>
+        </is>
+      </c>
+      <c r="C3" s="25" t="inlineStr">
+        <is>
+          <t>0 套</t>
+        </is>
+      </c>
+      <c r="D3" s="26" t="inlineStr">
+        <is>
+          <t>2 套</t>
+        </is>
+      </c>
+      <c r="E3" s="27" t="inlineStr">
+        <is>
+          <t>0 套</t>
+        </is>
+      </c>
+      <c r="F3" s="23" t="inlineStr">
+        <is>
+          <t>0 套</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="25" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>类型/位置</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>21号屋</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>22号屋</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="80" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>独立屋</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>21号屋
+6326呎 (3房)
+(19年-08月)
+$5.39亿
+$85,188/呎</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>22号屋
+7008呎 (4+房)
+(19年-09月)
+$5.81亿
+$82,889/呎</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/files/港岛-山顶区-Mount Nicholson II.xlsx
+++ b/files/港岛-山顶区-Mount Nicholson II.xlsx
@@ -691,7 +691,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>

--- a/files/港岛-山顶区-Mount Nicholson II.xlsx
+++ b/files/港岛-山顶区-Mount Nicholson II.xlsx
@@ -681,7 +681,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J28"/>
+  <dimension ref="A1:N28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -694,6 +694,10 @@
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -751,6 +755,26 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
+          <t>最高折扣</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>折实总价 (港币)</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>折实呎价 (港币/呎)</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>付款办法</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
           <t>是否招标</t>
         </is>
       </c>
@@ -797,6 +821,26 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -843,6 +887,26 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -889,6 +953,26 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -935,6 +1019,26 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -981,6 +1085,26 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1027,6 +1151,26 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1073,6 +1217,26 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1119,6 +1283,26 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1165,6 +1349,26 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1211,6 +1415,26 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1257,6 +1481,26 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1307,6 +1551,26 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1353,6 +1617,26 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1399,6 +1683,26 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1445,6 +1749,26 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1491,6 +1815,26 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1537,6 +1881,26 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1583,6 +1947,26 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1629,6 +2013,26 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1675,6 +2079,26 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1721,6 +2145,26 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1767,6 +2211,26 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1813,6 +2277,26 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1859,6 +2343,26 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1905,6 +2409,26 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1951,13 +2475,33 @@
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -2077,7 +2621,7 @@
           <t>- | 4493呎 (4+房)
 $91200万
 $202,982/呎
-(16年-11月)</t>
+(16年-11月-07日)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr"/>
@@ -2093,7 +2637,7 @@
           <t>- | 4538呎 (4+房)
 $68578万
 $151,119/呎
-(16年-10月)</t>
+(16年-10月-19日)</t>
         </is>
       </c>
       <c r="C6" s="21" t="inlineStr"/>
@@ -2109,7 +2653,7 @@
           <t>- | 4548呎 (4+房)
 $74902万
 $164,692/呎
-(16年-10月)</t>
+(16年-10月-27日)</t>
         </is>
       </c>
       <c r="C7" s="21" t="inlineStr"/>
@@ -2125,7 +2669,7 @@
           <t>- | 4566呎 (4+房)
 $65200万
 $142,795/呎
-(16年-10月)</t>
+(16年-10月-19日)</t>
         </is>
       </c>
       <c r="C8" s="21" t="inlineStr"/>
@@ -2141,7 +2685,7 @@
           <t>- | 4566呎 (4+房)
 $64464万
 $141,184/呎
-(16年-10月)</t>
+(16年-10月-19日)</t>
         </is>
       </c>
       <c r="C9" s="21" t="inlineStr"/>
@@ -2157,7 +2701,7 @@
           <t>- | 4566呎 (4+房)
 $64642万
 $141,571/呎
-(16年-10月)</t>
+(16年-10月-19日)</t>
         </is>
       </c>
       <c r="C10" s="21" t="inlineStr"/>
@@ -2173,7 +2717,7 @@
           <t>- | 4566呎 (4+房)
 $35039万
 $76,739/呎
-(16年-11月)</t>
+(16年-11月-07日)</t>
         </is>
       </c>
       <c r="C11" s="21" t="inlineStr"/>
@@ -2189,7 +2733,7 @@
           <t>- | 4566呎 (4+房)
 $31200万
 $68,331/呎
-(16年-12月)</t>
+(16年-12月-08日)</t>
         </is>
       </c>
       <c r="C12" s="21" t="inlineStr"/>
@@ -2205,7 +2749,7 @@
           <t>- | 4566呎 (4+房)
 $59328万
 $129,935/呎
-(17年-01月)</t>
+(17年-01月-17日)</t>
         </is>
       </c>
       <c r="C13" s="21" t="inlineStr"/>
@@ -2221,7 +2765,7 @@
           <t>- | 4566呎 (4+房)
 $30820万
 $67,500/呎
-(17年-02月)</t>
+(17年-02月-22日)</t>
         </is>
       </c>
       <c r="C14" s="21" t="inlineStr"/>
@@ -2237,7 +2781,7 @@
           <t>- | 4569呎 (4+房)
 $56800万
 $124,316/呎
-(17年-03月)</t>
+(17年-03月-19日)</t>
         </is>
       </c>
       <c r="C15" s="21" t="inlineStr"/>
@@ -2380,7 +2924,7 @@
           <t>- | 4209呎 (4+房)
 $91200万
 $216,679/呎
-(16年-11月)</t>
+(16年-11月-07日)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr"/>
@@ -2396,7 +2940,7 @@
           <t>- | 4254呎 (4+房)
 $68578万
 $161,207/呎
-(16年-10月)</t>
+(16年-10月-19日)</t>
         </is>
       </c>
       <c r="C6" s="21" t="inlineStr"/>
@@ -2412,7 +2956,7 @@
           <t>- | 4264呎 (4+房)
 $38000万
 $89,118/呎
-(20年-04月)</t>
+(20年-04月-28日)</t>
         </is>
       </c>
       <c r="C7" s="21" t="inlineStr"/>
@@ -2428,7 +2972,7 @@
           <t>- | 4289呎 (4+房)
 $65200万
 $152,017/呎
-(16年-10月)</t>
+(16年-10月-19日)</t>
         </is>
       </c>
       <c r="C8" s="21" t="inlineStr"/>
@@ -2444,7 +2988,7 @@
           <t>- | 4289呎 (4+房)
 $64464万
 $150,302/呎
-(16年-10月)</t>
+(16年-10月-19日)</t>
         </is>
       </c>
       <c r="C9" s="21" t="inlineStr"/>
@@ -2460,7 +3004,7 @@
           <t>- | 4289呎 (4+房)
 $64642万
 $150,715/呎
-(16年-10月)</t>
+(16年-10月-19日)</t>
         </is>
       </c>
       <c r="C10" s="21" t="inlineStr"/>
@@ -2476,7 +3020,7 @@
           <t>- | 4289呎 (4+房)
 $31653万
 $73,800/呎
-(16年-12月)</t>
+(16年-12月-13日)</t>
         </is>
       </c>
       <c r="C11" s="21" t="inlineStr"/>
@@ -2492,7 +3036,7 @@
           <t>- | 4289呎 (4+房)
 $27278万
 $63,600/呎
-(16年-11月)</t>
+(16年-11月-13日)</t>
         </is>
       </c>
       <c r="C12" s="21" t="inlineStr"/>
@@ -2508,7 +3052,7 @@
           <t>- | 4289呎 (4+房)
 $59328万
 $138,327/呎
-(17年-01月)</t>
+(17年-01月-17日)</t>
         </is>
       </c>
       <c r="C13" s="21" t="inlineStr"/>
@@ -2524,7 +3068,7 @@
           <t>- | 4289呎 (4+房)
 $28736万
 $66,999/呎
-(17年-07月)</t>
+(17年-07月-13日)</t>
         </is>
       </c>
       <c r="C14" s="21" t="inlineStr"/>
@@ -2540,7 +3084,7 @@
           <t>- | 4281呎 (4+房)
 $56800万
 $132,679/呎
-(17年-03月)</t>
+(17年-03月-19日)</t>
         </is>
       </c>
       <c r="C15" s="21" t="inlineStr"/>
@@ -2557,7 +3101,7 @@
           <t>B | 4217呎 (4+房)
 $60900万
 $144,415/呎
-(25年-06月)</t>
+(25年-06月-08日)</t>
         </is>
       </c>
     </row>
@@ -2682,7 +3226,7 @@
         <is>
           <t>21号屋
 6326呎 (3房)
-(19年-08月)
+(19年-08月-01日)
 $5.39亿
 $85,188/呎</t>
         </is>
@@ -2691,7 +3235,7 @@
         <is>
           <t>22号屋
 7008呎 (4+房)
-(19年-09月)
+(19年-09月-12日)
 $5.81亿
 $82,889/呎</t>
         </is>

--- a/files/港岛-山顶区-Mount Nicholson II.xlsx
+++ b/files/港岛-山顶区-Mount Nicholson II.xlsx
@@ -2621,7 +2621,7 @@
           <t>- | 4493呎 (4+房)
 $91200万
 $202,982/呎
-(16年-11月-07日)</t>
+(16年-11月)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr"/>
@@ -2637,7 +2637,7 @@
           <t>- | 4538呎 (4+房)
 $68578万
 $151,119/呎
-(16年-10月-19日)</t>
+(16年-10月)</t>
         </is>
       </c>
       <c r="C6" s="21" t="inlineStr"/>
@@ -2653,7 +2653,7 @@
           <t>- | 4548呎 (4+房)
 $74902万
 $164,692/呎
-(16年-10月-27日)</t>
+(16年-10月)</t>
         </is>
       </c>
       <c r="C7" s="21" t="inlineStr"/>
@@ -2669,7 +2669,7 @@
           <t>- | 4566呎 (4+房)
 $65200万
 $142,795/呎
-(16年-10月-19日)</t>
+(16年-10月)</t>
         </is>
       </c>
       <c r="C8" s="21" t="inlineStr"/>
@@ -2685,7 +2685,7 @@
           <t>- | 4566呎 (4+房)
 $64464万
 $141,184/呎
-(16年-10月-19日)</t>
+(16年-10月)</t>
         </is>
       </c>
       <c r="C9" s="21" t="inlineStr"/>
@@ -2701,7 +2701,7 @@
           <t>- | 4566呎 (4+房)
 $64642万
 $141,571/呎
-(16年-10月-19日)</t>
+(16年-10月)</t>
         </is>
       </c>
       <c r="C10" s="21" t="inlineStr"/>
@@ -2717,7 +2717,7 @@
           <t>- | 4566呎 (4+房)
 $35039万
 $76,739/呎
-(16年-11月-07日)</t>
+(16年-11月)</t>
         </is>
       </c>
       <c r="C11" s="21" t="inlineStr"/>
@@ -2733,7 +2733,7 @@
           <t>- | 4566呎 (4+房)
 $31200万
 $68,331/呎
-(16年-12月-08日)</t>
+(16年-12月)</t>
         </is>
       </c>
       <c r="C12" s="21" t="inlineStr"/>
@@ -2749,7 +2749,7 @@
           <t>- | 4566呎 (4+房)
 $59328万
 $129,935/呎
-(17年-01月-17日)</t>
+(17年-01月)</t>
         </is>
       </c>
       <c r="C13" s="21" t="inlineStr"/>
@@ -2765,7 +2765,7 @@
           <t>- | 4566呎 (4+房)
 $30820万
 $67,500/呎
-(17年-02月-22日)</t>
+(17年-02月)</t>
         </is>
       </c>
       <c r="C14" s="21" t="inlineStr"/>
@@ -2781,7 +2781,7 @@
           <t>- | 4569呎 (4+房)
 $56800万
 $124,316/呎
-(17年-03月-19日)</t>
+(17年-03月)</t>
         </is>
       </c>
       <c r="C15" s="21" t="inlineStr"/>
@@ -2924,7 +2924,7 @@
           <t>- | 4209呎 (4+房)
 $91200万
 $216,679/呎
-(16年-11月-07日)</t>
+(16年-11月)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr"/>
@@ -2940,7 +2940,7 @@
           <t>- | 4254呎 (4+房)
 $68578万
 $161,207/呎
-(16年-10月-19日)</t>
+(16年-10月)</t>
         </is>
       </c>
       <c r="C6" s="21" t="inlineStr"/>
@@ -2956,7 +2956,7 @@
           <t>- | 4264呎 (4+房)
 $38000万
 $89,118/呎
-(20年-04月-28日)</t>
+(20年-04月)</t>
         </is>
       </c>
       <c r="C7" s="21" t="inlineStr"/>
@@ -2972,7 +2972,7 @@
           <t>- | 4289呎 (4+房)
 $65200万
 $152,017/呎
-(16年-10月-19日)</t>
+(16年-10月)</t>
         </is>
       </c>
       <c r="C8" s="21" t="inlineStr"/>
@@ -2988,7 +2988,7 @@
           <t>- | 4289呎 (4+房)
 $64464万
 $150,302/呎
-(16年-10月-19日)</t>
+(16年-10月)</t>
         </is>
       </c>
       <c r="C9" s="21" t="inlineStr"/>
@@ -3004,7 +3004,7 @@
           <t>- | 4289呎 (4+房)
 $64642万
 $150,715/呎
-(16年-10月-19日)</t>
+(16年-10月)</t>
         </is>
       </c>
       <c r="C10" s="21" t="inlineStr"/>
@@ -3020,7 +3020,7 @@
           <t>- | 4289呎 (4+房)
 $31653万
 $73,800/呎
-(16年-12月-13日)</t>
+(16年-12月)</t>
         </is>
       </c>
       <c r="C11" s="21" t="inlineStr"/>
@@ -3036,7 +3036,7 @@
           <t>- | 4289呎 (4+房)
 $27278万
 $63,600/呎
-(16年-11月-13日)</t>
+(16年-11月)</t>
         </is>
       </c>
       <c r="C12" s="21" t="inlineStr"/>
@@ -3052,7 +3052,7 @@
           <t>- | 4289呎 (4+房)
 $59328万
 $138,327/呎
-(17年-01月-17日)</t>
+(17年-01月)</t>
         </is>
       </c>
       <c r="C13" s="21" t="inlineStr"/>
@@ -3068,7 +3068,7 @@
           <t>- | 4289呎 (4+房)
 $28736万
 $66,999/呎
-(17年-07月-13日)</t>
+(17年-07月)</t>
         </is>
       </c>
       <c r="C14" s="21" t="inlineStr"/>
@@ -3084,7 +3084,7 @@
           <t>- | 4281呎 (4+房)
 $56800万
 $132,679/呎
-(17年-03月-19日)</t>
+(17年-03月)</t>
         </is>
       </c>
       <c r="C15" s="21" t="inlineStr"/>
@@ -3101,7 +3101,7 @@
           <t>B | 4217呎 (4+房)
 $60900万
 $144,415/呎
-(25年-06月-08日)</t>
+(25年-06月)</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
         <is>
           <t>21号屋
 6326呎 (3房)
-(19年-08月-01日)
+(19年-08月)
 $5.39亿
 $85,188/呎</t>
         </is>
@@ -3235,7 +3235,7 @@
         <is>
           <t>22号屋
 7008呎 (4+房)
-(19年-09月-12日)
+(19年-09月)
 $5.81亿
 $82,889/呎</t>
         </is>

--- a/files/港岛-山顶区-Mount Nicholson II.xlsx
+++ b/files/港岛-山顶区-Mount Nicholson II.xlsx
@@ -2621,7 +2621,7 @@
           <t>- | 4493呎 (4+房)
 $91200万
 $202,982/呎
-(16年-11月)</t>
+(16年-11月-07日)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr"/>
@@ -2637,7 +2637,7 @@
           <t>- | 4538呎 (4+房)
 $68578万
 $151,119/呎
-(16年-10月)</t>
+(16年-10月-19日)</t>
         </is>
       </c>
       <c r="C6" s="21" t="inlineStr"/>
@@ -2653,7 +2653,7 @@
           <t>- | 4548呎 (4+房)
 $74902万
 $164,692/呎
-(16年-10月)</t>
+(16年-10月-27日)</t>
         </is>
       </c>
       <c r="C7" s="21" t="inlineStr"/>
@@ -2669,7 +2669,7 @@
           <t>- | 4566呎 (4+房)
 $65200万
 $142,795/呎
-(16年-10月)</t>
+(16年-10月-19日)</t>
         </is>
       </c>
       <c r="C8" s="21" t="inlineStr"/>
@@ -2685,7 +2685,7 @@
           <t>- | 4566呎 (4+房)
 $64464万
 $141,184/呎
-(16年-10月)</t>
+(16年-10月-19日)</t>
         </is>
       </c>
       <c r="C9" s="21" t="inlineStr"/>
@@ -2701,7 +2701,7 @@
           <t>- | 4566呎 (4+房)
 $64642万
 $141,571/呎
-(16年-10月)</t>
+(16年-10月-19日)</t>
         </is>
       </c>
       <c r="C10" s="21" t="inlineStr"/>
@@ -2717,7 +2717,7 @@
           <t>- | 4566呎 (4+房)
 $35039万
 $76,739/呎
-(16年-11月)</t>
+(16年-11月-07日)</t>
         </is>
       </c>
       <c r="C11" s="21" t="inlineStr"/>
@@ -2733,7 +2733,7 @@
           <t>- | 4566呎 (4+房)
 $31200万
 $68,331/呎
-(16年-12月)</t>
+(16年-12月-08日)</t>
         </is>
       </c>
       <c r="C12" s="21" t="inlineStr"/>
@@ -2749,7 +2749,7 @@
           <t>- | 4566呎 (4+房)
 $59328万
 $129,935/呎
-(17年-01月)</t>
+(17年-01月-17日)</t>
         </is>
       </c>
       <c r="C13" s="21" t="inlineStr"/>
@@ -2765,7 +2765,7 @@
           <t>- | 4566呎 (4+房)
 $30820万
 $67,500/呎
-(17年-02月)</t>
+(17年-02月-22日)</t>
         </is>
       </c>
       <c r="C14" s="21" t="inlineStr"/>
@@ -2781,7 +2781,7 @@
           <t>- | 4569呎 (4+房)
 $56800万
 $124,316/呎
-(17年-03月)</t>
+(17年-03月-19日)</t>
         </is>
       </c>
       <c r="C15" s="21" t="inlineStr"/>
@@ -2924,7 +2924,7 @@
           <t>- | 4209呎 (4+房)
 $91200万
 $216,679/呎
-(16年-11月)</t>
+(16年-11月-07日)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr"/>
@@ -2940,7 +2940,7 @@
           <t>- | 4254呎 (4+房)
 $68578万
 $161,207/呎
-(16年-10月)</t>
+(16年-10月-19日)</t>
         </is>
       </c>
       <c r="C6" s="21" t="inlineStr"/>
@@ -2956,7 +2956,7 @@
           <t>- | 4264呎 (4+房)
 $38000万
 $89,118/呎
-(20年-04月)</t>
+(20年-04月-28日)</t>
         </is>
       </c>
       <c r="C7" s="21" t="inlineStr"/>
@@ -2972,7 +2972,7 @@
           <t>- | 4289呎 (4+房)
 $65200万
 $152,017/呎
-(16年-10月)</t>
+(16年-10月-19日)</t>
         </is>
       </c>
       <c r="C8" s="21" t="inlineStr"/>
@@ -2988,7 +2988,7 @@
           <t>- | 4289呎 (4+房)
 $64464万
 $150,302/呎
-(16年-10月)</t>
+(16年-10月-19日)</t>
         </is>
       </c>
       <c r="C9" s="21" t="inlineStr"/>
@@ -3004,7 +3004,7 @@
           <t>- | 4289呎 (4+房)
 $64642万
 $150,715/呎
-(16年-10月)</t>
+(16年-10月-19日)</t>
         </is>
       </c>
       <c r="C10" s="21" t="inlineStr"/>
@@ -3020,7 +3020,7 @@
           <t>- | 4289呎 (4+房)
 $31653万
 $73,800/呎
-(16年-12月)</t>
+(16年-12月-13日)</t>
         </is>
       </c>
       <c r="C11" s="21" t="inlineStr"/>
@@ -3036,7 +3036,7 @@
           <t>- | 4289呎 (4+房)
 $27278万
 $63,600/呎
-(16年-11月)</t>
+(16年-11月-13日)</t>
         </is>
       </c>
       <c r="C12" s="21" t="inlineStr"/>
@@ -3052,7 +3052,7 @@
           <t>- | 4289呎 (4+房)
 $59328万
 $138,327/呎
-(17年-01月)</t>
+(17年-01月-17日)</t>
         </is>
       </c>
       <c r="C13" s="21" t="inlineStr"/>
@@ -3068,7 +3068,7 @@
           <t>- | 4289呎 (4+房)
 $28736万
 $66,999/呎
-(17年-07月)</t>
+(17年-07月-13日)</t>
         </is>
       </c>
       <c r="C14" s="21" t="inlineStr"/>
@@ -3084,7 +3084,7 @@
           <t>- | 4281呎 (4+房)
 $56800万
 $132,679/呎
-(17年-03月)</t>
+(17年-03月-19日)</t>
         </is>
       </c>
       <c r="C15" s="21" t="inlineStr"/>
@@ -3101,7 +3101,7 @@
           <t>B | 4217呎 (4+房)
 $60900万
 $144,415/呎
-(25年-06月)</t>
+(25年-06月-08日)</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
         <is>
           <t>21号屋
 6326呎 (3房)
-(19年-08月)
+(19年-08月-01日)
 $5.39亿
 $85,188/呎</t>
         </is>
@@ -3235,7 +3235,7 @@
         <is>
           <t>22号屋
 7008呎 (4+房)
-(19年-09月)
+(19年-09月-12日)
 $5.81亿
 $82,889/呎</t>
         </is>
